--- a/OUTPUT/direct_P0A7C2_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/OUTPUT/direct_P0A7C2_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.5028</v>
+        <v>0.5027988804478208</v>
       </c>
     </row>
   </sheetData>
